--- a/dataset_t6_grouped/results2/G5/G5_T2372_W0066F0002T0006Z000C1N11_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G5/G5_T2372_W0066F0002T0006Z000C1N11_analysis.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H3"/>
+  <dimension ref="A1:H4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -486,10 +486,10 @@
         <v>21.68115411130957</v>
       </c>
       <c r="E2" t="n">
-        <v>3.240512782699991</v>
+        <v>8.31712269456518</v>
       </c>
       <c r="F2" t="n">
-        <v>2.792383381940594</v>
+        <v>7.727665813865268</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -518,10 +518,10 @@
         <v>27.26592087519075</v>
       </c>
       <c r="E3" t="n">
-        <v>3.240512782699991</v>
+        <v>8.31712269456518</v>
       </c>
       <c r="F3" t="n">
-        <v>2.792383381940594</v>
+        <v>7.727665813865268</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -529,6 +529,38 @@
         </is>
       </c>
       <c r="H3" t="inlineStr">
+        <is>
+          <t>G5</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>W0066F0002T0006Z000C1N11.png</t>
+        </is>
+      </c>
+      <c r="B4" t="n">
+        <v>3</v>
+      </c>
+      <c r="C4" t="n">
+        <v>8.248934031516065</v>
+      </c>
+      <c r="D4" t="n">
+        <v>8.810412953960283</v>
+      </c>
+      <c r="E4" t="n">
+        <v>8.31712269456518</v>
+      </c>
+      <c r="F4" t="n">
+        <v>7.727665813865268</v>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>T2372</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
         <is>
           <t>G5</t>
         </is>

--- a/dataset_t6_grouped/results2/G5/G5_T2372_W0066F0002T0006Z000C1N11_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G5/G5_T2372_W0066F0002T0006Z000C1N11_analysis.xlsx
@@ -480,16 +480,16 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>21.73512490911639</v>
+        <v>3.531957797731414</v>
       </c>
       <c r="D2" t="n">
-        <v>21.68115411130957</v>
+        <v>3.523187543087805</v>
       </c>
       <c r="E2" t="n">
-        <v>8.31712269456518</v>
+        <v>1.351532437866842</v>
       </c>
       <c r="F2" t="n">
-        <v>7.727665813865268</v>
+        <v>1.255745694753106</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -512,16 +512,16 @@
         <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>28.21615047451638</v>
+        <v>4.585124452108911</v>
       </c>
       <c r="D3" t="n">
-        <v>27.26592087519075</v>
+        <v>4.430712142218498</v>
       </c>
       <c r="E3" t="n">
-        <v>8.31712269456518</v>
+        <v>1.351532437866842</v>
       </c>
       <c r="F3" t="n">
-        <v>7.727665813865268</v>
+        <v>1.255745694753106</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -544,16 +544,16 @@
         <v>3</v>
       </c>
       <c r="C4" t="n">
-        <v>8.248934031516065</v>
+        <v>1.34045178012136</v>
       </c>
       <c r="D4" t="n">
-        <v>8.810412953960283</v>
+        <v>1.431692105018546</v>
       </c>
       <c r="E4" t="n">
-        <v>8.31712269456518</v>
+        <v>1.351532437866842</v>
       </c>
       <c r="F4" t="n">
-        <v>7.727665813865268</v>
+        <v>1.255745694753106</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
